--- a/AlphaForge_Fineco_Advisor_Questions.xlsx
+++ b/AlphaForge_Fineco_Advisor_Questions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,12 +564,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ESEMPIO_CORE</t>
+          <t>LU0981915779</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Per ESEMPIO_CORE: qual e' il ruolo nel portafoglio e con quale ETF/fondo lo confrontiamo?</t>
+          <t>Per LU0981915779: quale peso massimo satellite e cosa deve succedere per aumentare/ridurre?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -584,15 +584,115 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ESEMPIO_PAC</t>
+          <t>IE0005TOUMC7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Per ESEMPIO_PAC: quando parte la prima rata PAC e quale benchmark useriamo per valutarlo?</t>
+          <t>Per IE0005TOUMC7: quali sottostanti, costi totali e sovrapposizione con All-World/MSCI World?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
+        <is>
+          <t>Domanda specifica sul singolo strumento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>IE000KTYLDC4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Per IE000KTYLDC4: quali sottostanti, costi totali e sovrapposizione con All-World/MSCI World?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Domanda specifica sul singolo strumento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LU0261952682</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Per LU0261952682: quale peso massimo satellite e cosa deve succedere per aumentare/ridurre?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Domanda specifica sul singolo strumento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>IE000DWG3DP6</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Per IE000DWG3DP6: quali sottostanti, costi totali e sovrapposizione con All-World/MSCI World?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Domanda specifica sul singolo strumento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>IE0003YRHWF4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Per IE0003YRHWF4: quando parte la prima rata PAC e quale benchmark useriamo per valutarlo?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Domanda specifica sul singolo strumento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>IE00BD2PJG29</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Per IE00BD2PJG29: quando parte la prima rata PAC e quale benchmark useriamo per valutarlo?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Domanda specifica sul singolo strumento.</t>
         </is>
